--- a/Raw.Data/WW_Seedlings_2025.xlsx
+++ b/Raw.Data/WW_Seedlings_2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://holdenarb-my.sharepoint.com/personal/sworthy_holdenfg_org/Documents/Documents/GitHub/LTREB/Raw.Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="907" documentId="8_{EEC2CD84-A99A-4B44-8145-845B4822B097}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B7A68862-AFD7-4799-BCDB-51F4B8E0CE37}"/>
+  <xr:revisionPtr revIDLastSave="909" documentId="8_{EEC2CD84-A99A-4B44-8145-845B4822B097}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FA935EA9-CFB5-497D-A11A-9F8BDBAF679F}"/>
   <bookViews>
-    <workbookView xWindow="864" yWindow="1308" windowWidth="17364" windowHeight="10392" activeTab="1" xr2:uid="{4134154B-C6FD-416F-B23E-801437174979}"/>
+    <workbookView xWindow="0" yWindow="1080" windowWidth="23040" windowHeight="11160" activeTab="1" xr2:uid="{4134154B-C6FD-416F-B23E-801437174979}"/>
   </bookViews>
   <sheets>
     <sheet name="WW_Recruitment_BirdBands_e2025_" sheetId="1" r:id="rId1"/>
@@ -41152,6 +41152,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="616c080f-25a0-4195-acea-d0f9cb6dd160">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <Notes xmlns="616c080f-25a0-4195-acea-d0f9cb6dd160" xsi:nil="true"/>
+    <TaxCatchAll xmlns="2925ced4-9649-4694-8b02-7b2baada13be" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D2EC6BD01720AE40890B06D73BA7FBB3" ma:contentTypeVersion="19" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="1f943927feae1788057954499264f76e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="616c080f-25a0-4195-acea-d0f9cb6dd160" xmlns:ns3="2925ced4-9649-4694-8b02-7b2baada13be" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="cb09de3a1b56f2bbf7a9e04c8c94fc0e" ns2:_="" ns3:_="">
     <xsd:import namespace="616c080f-25a0-4195-acea-d0f9cb6dd160"/>
@@ -41414,18 +41426,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="616c080f-25a0-4195-acea-d0f9cb6dd160">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <Notes xmlns="616c080f-25a0-4195-acea-d0f9cb6dd160" xsi:nil="true"/>
-    <TaxCatchAll xmlns="2925ced4-9649-4694-8b02-7b2baada13be" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C07FFA48-3144-4CC6-A927-6342691A04C5}">
   <ds:schemaRefs>
@@ -41435,6 +41435,17 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CE4FCCFE-694E-4535-8D06-F587E55459BF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="616c080f-25a0-4195-acea-d0f9cb6dd160"/>
+    <ds:schemaRef ds:uri="2925ced4-9649-4694-8b02-7b2baada13be"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{39310D14-59B3-4392-A105-72338788B294}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -41451,15 +41462,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CE4FCCFE-694E-4535-8D06-F587E55459BF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="616c080f-25a0-4195-acea-d0f9cb6dd160"/>
-    <ds:schemaRef ds:uri="2925ced4-9649-4694-8b02-7b2baada13be"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>